--- a/pcb/af4-trigger-hat-centroid.xlsx
+++ b/pcb/af4-trigger-hat-centroid.xlsx
@@ -49,9 +49,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -455,459 +460,459 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>43.450</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>35.500</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>180.0</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>49.350</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>26.000</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>180.0</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>39.050</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>42.500</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>90.0</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>39.050</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>33.500</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>270.0</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>50.350</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>21.000</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>180.0</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>40.750</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>4.000</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>39.050</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>9.200</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>90.0</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>40.350</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>48.000</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>180.0</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>31.350</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>28.000</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>22.850</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>27.890</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>39.050</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>16.700</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>90.0</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>53.850</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>27.000</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>180.0</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>R5</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>53.850</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>24.000</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>R6</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>46.850</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>21.000</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>39.050</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>12.800</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>270.0</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>U1</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>34.850</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>23.000</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>U2</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>51.850</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>32.500</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>180.0</t>
         </is>
